--- a/data/paises_extra/por_pais/Gobernanza_PT_Portugal_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_PT_Portugal_ILIA2026.xlsx
@@ -597,7 +597,8 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250</t>
         </is>
       </c>
     </row>
@@ -624,13 +625,13 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>ANIA publicada en enero 2026 → tramo 2024-26.  [confianza: ALTA]
-Nota matriz: EE: White Paper 2024-30 · SG: Update NAIS may-2026 = estrategia vigente (decisión operador) · DE: Aktionsplan 2023 · ES: Estrategia 2024 · PT: ANIA 2026-30</t>
+          <t>ANIA publicada en enero 2026 → tramo 2024-26.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gov.pt</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
         </is>
       </c>
     </row>
@@ -662,7 +663,8 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>https://cms.law</t>
+          <t>https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
+https://www.incode2030.gov.pt/en/estrategia-nacional-de-inteligencia-artificial-en/</t>
         </is>
       </c>
     </row>
@@ -694,7 +696,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>https://www.adcecija.pt</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -721,13 +723,13 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>&gt;€400M hasta 2030 (+€25M sector público).  [confianza: ALTA]
-Nota matriz: EE €85M · SG &gt;S$1.000M · DE €5.000M · ES €1.500M · PT &gt;€400M</t>
+          <t>&gt;€400M hasta 2030 (+€25M sector público).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>https://www.rtp.pt</t>
+          <t>https://www.portugal.gov.pt/pt/gc25/comunicacao/noticia?i=inteligencia-artificial-governo-lanca-agenda-nacional-com-mais-de-400-milhoes-de-euros
+https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
         </is>
       </c>
     </row>
@@ -759,7 +761,8 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026</t>
         </is>
       </c>
     </row>
@@ -791,7 +794,8 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>https://www.abreuadvogados.com</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/</t>
         </is>
       </c>
     </row>
@@ -823,7 +827,8 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>https://www.compete2030.gov.pt</t>
+          <t>https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/
+https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -855,7 +860,8 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>https://www.timestampgroup.com</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/</t>
         </is>
       </c>
     </row>
@@ -887,7 +893,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>https://www.adcecija.pt</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -919,7 +925,8 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>https://www.rtp.pt</t>
+          <t>https://www.portugal.gov.pt/pt/gc25/comunicacao/noticia?i=inteligencia-artificial-governo-lanca-agenda-nacional-com-mais-de-400-milhoes-de-euros
+https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
         </is>
       </c>
     </row>
@@ -951,7 +958,8 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://www.compete2030.gov.pt</t>
+          <t>https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/
+https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -983,7 +991,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/national/portugal</t>
+          <t>https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250
+https://www.incode2030.gov.pt/en/estrategia-nacional-de-inteligencia-artificial-en/</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1024,8 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>https://www.oecd.org</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+https://oecd.ai/en/ai-principles</t>
         </is>
       </c>
     </row>
@@ -1042,13 +1052,13 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>No verificado como eje en la ANIA (solo principio en la EDN) → 0. PRELIM.  [confianza: MEDIA · PRELIM]
-Nota matriz: Solo ES recoge género (mención transversal); resto NO ENCONTRADO/0</t>
+          <t>No verificado como eje en la ANIA (solo principio en la EDN) → 0. PRELIM.  [confianza: MEDIA · PRELIM]</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gov.pt</t>
+          <t>https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
+https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -1075,13 +1085,13 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>No verificado como eje en la ANIA (solo principio en la EDN) → 0. PRELIM.  [confianza: MEDIA · PRELIM]
-Nota matriz: PT: solo principio en EDN, no eje en ANIA</t>
+          <t>No verificado como eje en la ANIA (solo principio en la EDN) → 0. PRELIM.  [confianza: MEDIA · PRELIM]</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gov.pt</t>
+          <t>https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
+https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -1108,13 +1118,13 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>3 sesiones públicas + participa.gov.pt + consultalex; resultados incorporados → 4.  [confianza: ALTA]
-Nota matriz: PT: consulta pública con resultados</t>
+          <t>3 sesiones públicas (Lisboa/Évora/Porto) + participa.gov.pt + consultalex; resultados incorporados → 4.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://www.portugal.gov.pt</t>
+          <t>https://digital.gov.pt/noticias/roteiro-de-auscultacao-sobre-a-agenda-nacional-de-ia-arranca-em-janeiro
+https://www.portugal.gov.pt/pt/gc24/comunicacao/noticia?i=auscultacao-para-a-agenda-nacional-de-inteligencia-artificial-inicia-se-esta-semana</t>
         </is>
       </c>
     </row>
@@ -1141,14 +1151,13 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Elaboración: Gob + academia + empresas/startups + AP + ciudadanos (Gob+4).  [confianza: ALTA]
-Nota matriz: PT: Gob+4</t>
+          <t>Elaboración: Gob + academia + empresas/startups + AP + ciudadanos (Gob+4).  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>https://cms.law
-https://www.pra.pt</t>
+          <t>https://www.portugal.gov.pt/pt/gc24/comunicacao/noticia?i=auscultacao-para-a-agenda-nacional-de-inteligencia-artificial-inicia-se-esta-semana
+https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1189,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://www.timestampgroup.com</t>
+          <t>https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/</t>
         </is>
       </c>
     </row>
@@ -1207,14 +1216,14 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>&gt;1 institución: AMA (coord.) + FCT + ANACOM (autoridad AI Act) + INCoDe.2030 + CNPD.  [confianza: ALTA]
-Nota matriz: ES: SEDIA+AESIA · DE: 3 min+PLS+BNetzA · PT: AMA+FCT+ANACOM</t>
+          <t>&gt;1 institución: AMA (coord.) + FCT + ANACOM (autoridad AI Act) + INCoDe.2030 + CNPD.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/national/portugal
-https://cms.law</t>
+          <t>https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250
+https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791
+https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1255,7 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>https://www.adcecija.pt</t>
+          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -1280,8 +1289,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Observador (O-member, IPQ) en SC 42 → 1.  [confianza: ALTA]
-Nota matriz: EE: no figura (verificar) · PT: Observador</t>
+          <t>Observador (O-member, IPQ) en SC 42 → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -1314,8 +1322,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Observador (O-member, IPQ) en SC 27 → 1.  [confianza: ALTA]
-Nota matriz: PT: Observador</t>
+          <t>Observador (O-member, IPQ) en SC 27 → 1.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -1347,8 +1354,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>OECD AI Principles + UNESCO + EU Coordinated Plan (CoE vía UE) = 2+. GPAI: PT no es miembro individual.  [confianza: ALTA]
-Nota matriz: GPAI: miembros DE/ES; EE/SG/PT no individual</t>
+          <t>OECD AI Principles + UNESCO + EU Coordinated Plan (CoE vía UE) = 2+. GPAI: PT no es miembro individual.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -1388,13 +1394,14 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>EU AI Act; ANACOM designada autoridad (sept-2025); sin ley nacional autónoma.  [confianza: ALTA]
-Nota matriz: UE: EU AI Act (EE/DE/ES/PT). SG: soft law=1. ES/DE: además ley nacional</t>
+          <t>EU AI Act; ANACOM designada autoridad (sept-2025); sin ley nacional autónoma.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>https://cms.law</t>
+          <t>https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791
+https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal
+https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
         </is>
       </c>
     </row>
@@ -1453,13 +1460,13 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Obligación del EU AI Act (art. 57, ago-2026) bajo ANACOM. PRELIM.  [confianza: MEDIA-ALTA · PRELIM]
-Nota matriz: ES: 1er sandbox UE</t>
+          <t>Obligación del EU AI Act (art. 57, ago-2026) bajo ANACOM. PRELIM.  [confianza: MEDIA-ALTA · PRELIM]</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>https://artificialintelligenceact.eu/article/57</t>
+          <t>https://artificialintelligenceact.eu/article/57
+https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791</t>
         </is>
       </c>
     </row>
@@ -1519,8 +1526,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>CNPD.  [confianza: ALTA]
-Nota matriz: AKI/PDPC/BfDI/AEPD/CNPD</t>
+          <t>CNPD.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -1559,8 +1565,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>NO ENCONTRADO por pilar; GCI 2024 = Tier 1 (total ~99,86). Pilares solo en anexo PDF.  [confianza: MANUAL]
-Nota matriz: Solo ES con pilares; resto Tier 1, pilares en anexo PDF</t>
+          <t>NO ENCONTRADO por pilar; GCI 2024 = Tier 1 (total ~99,86). Pilares solo en anexo PDF.  [confianza: MANUAL]</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -1725,8 +1730,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>NO ENCONTRADO; PT cubierto por GIRAI; puntaje por área en portal JS/PDF.  [confianza: MANUAL]
-Nota matriz: Portal JS/PDF → extracción manual</t>
+          <t>NO ENCONTRADO; PT cubierto por GIRAI; puntaje por área en portal JS/PDF.  [confianza: MANUAL]</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -1758,8 +1762,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>NO ENCONTRADO (portal JS/PDF).  [confianza: MANUAL]
-Nota matriz: Idem</t>
+          <t>NO ENCONTRADO (portal JS/PDF).  [confianza: MANUAL]</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -1791,8 +1794,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>88,16 en 'Affordable &amp; clean energy' (overall NRI 61,54; rank 32), ed. 2025.  [confianza: MEDIA-ALTA]
-Nota matriz: ES: ver página país NRI</t>
+          <t>88,16 en 'Affordable &amp; clean energy' (overall NRI 61,54; rank 32), ed. 2025.  [confianza: MEDIA-ALTA]</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -1824,8 +1826,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>85,19 % (2024) / 80,95 % (2025) renovable total. Excl. toda hidro 53,69 %; hidro 31,50 % → si ILIA excluyera gran hidro, baja mucho.  [confianza: ALTA]
-Nota matriz: 2024, renovables total. ES/PT/DE: ERNC excl. gran hidro es menor (ver energia_*.md)</t>
+          <t>85,19 % (2024) / 80,95 % (2025) renovable total. Excl. toda hidro 53,69 %; hidro 31,50 % → si ILIA excluyera gran hidro, baja mucho.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">

--- a/data/paises_extra/por_pais/Gobernanza_PT_Portugal_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_PT_Portugal_ILIA2026.xlsx
@@ -525,7 +525,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Compendio exhaustivo de URLs: gobernanza/FUENTES_gobernanza_EE_SG.md (EE/SG) · gobernanza_&lt;país&gt;.md, gobernanza_estandares_*.md, etica_seguridad_*.md, energia_*.md (DE/ES/PT). Rúbricas: gobernanza/RUBRICAS_gobernanza.md.</t>
+          <t>Cada URL va etiquetada [oficial] (gobierno, BOE/Diário da República, ISO/ITU, OCDE, dato primario) o [secundaria] (prensa, despacho, agregador). Compendio exhaustivo: gobernanza/FUENTES_gobernanza_EE_SG.md (EE/SG) · gobernanza_&lt;país&gt;.md, gobernanza_estandares_*.md, etica_seguridad_*.md, energia_*.md (DE/ES/PT). Rúbricas: gobernanza/RUBRICAS_gobernanza.md.</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Fuentes y URLs</t>
+          <t>Fuentes y URLs  ([oficial] primaria · [secundaria] corrobora)</t>
         </is>
       </c>
     </row>
@@ -597,8 +597,8 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
-https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[oficial] https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250</t>
         </is>
       </c>
     </row>
@@ -630,8 +630,8 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
-https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[secundaria] https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
         </is>
       </c>
     </row>
@@ -663,8 +663,8 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
-https://www.incode2030.gov.pt/en/estrategia-nacional-de-inteligencia-artificial-en/</t>
+          <t>[oficial] https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
+[oficial] https://www.incode2030.gov.pt/en/estrategia-nacional-de-inteligencia-artificial-en/</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,8 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[oficial] https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026</t>
         </is>
       </c>
     </row>
@@ -728,8 +729,8 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>https://www.portugal.gov.pt/pt/gc25/comunicacao/noticia?i=inteligencia-artificial-governo-lanca-agenda-nacional-com-mais-de-400-milhoes-de-euros
-https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
+          <t>[oficial] https://www.portugal.gov.pt/pt/gc25/comunicacao/noticia?i=inteligencia-artificial-governo-lanca-agenda-nacional-com-mais-de-400-milhoes-de-euros
+[secundaria] https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
         </is>
       </c>
     </row>
@@ -761,8 +762,8 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
-https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[oficial] https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026</t>
         </is>
       </c>
     </row>
@@ -794,8 +795,8 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
-https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[oficial] https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/</t>
         </is>
       </c>
     </row>
@@ -827,8 +828,8 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/
-https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
+          <t>[oficial] https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/
+[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -860,8 +861,8 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
-https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[oficial] https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/</t>
         </is>
       </c>
     </row>
@@ -893,7 +894,8 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[oficial] https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026</t>
         </is>
       </c>
     </row>
@@ -925,8 +927,8 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>https://www.portugal.gov.pt/pt/gc25/comunicacao/noticia?i=inteligencia-artificial-governo-lanca-agenda-nacional-com-mais-de-400-milhoes-de-euros
-https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
+          <t>[oficial] https://www.portugal.gov.pt/pt/gc25/comunicacao/noticia?i=inteligencia-artificial-governo-lanca-agenda-nacional-com-mais-de-400-milhoes-de-euros
+[secundaria] https://observador.pt/2026/01/08/publicada-agenda-nacional-de-inteligencia-artificial-e-respetivo-plano-de-acao-ate-2030/</t>
         </is>
       </c>
     </row>
@@ -958,8 +960,8 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/
-https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
+          <t>[oficial] https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/
+[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -991,8 +993,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250
-https://www.incode2030.gov.pt/en/estrategia-nacional-de-inteligencia-artificial-en/</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250
+[oficial] https://www.incode2030.gov.pt/en/estrategia-nacional-de-inteligencia-artificial-en/</t>
         </is>
       </c>
     </row>
@@ -1024,8 +1026,8 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
-https://oecd.ai/en/ai-principles</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[oficial] https://oecd.ai/en/ai-principles</t>
         </is>
       </c>
     </row>
@@ -1057,8 +1059,8 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
-https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
+          <t>[oficial] https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
+[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -1090,8 +1092,8 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
-https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
+          <t>[oficial] https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026
+[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
         </is>
       </c>
     </row>
@@ -1123,8 +1125,8 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://digital.gov.pt/noticias/roteiro-de-auscultacao-sobre-a-agenda-nacional-de-ia-arranca-em-janeiro
-https://www.portugal.gov.pt/pt/gc24/comunicacao/noticia?i=auscultacao-para-a-agenda-nacional-de-inteligencia-artificial-inicia-se-esta-semana</t>
+          <t>[oficial] https://digital.gov.pt/noticias/roteiro-de-auscultacao-sobre-a-agenda-nacional-de-ia-arranca-em-janeiro
+[oficial] https://www.portugal.gov.pt/pt/gc24/comunicacao/noticia?i=auscultacao-para-a-agenda-nacional-de-inteligencia-artificial-inicia-se-esta-semana</t>
         </is>
       </c>
     </row>
@@ -1156,8 +1158,8 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>https://www.portugal.gov.pt/pt/gc24/comunicacao/noticia?i=auscultacao-para-a-agenda-nacional-de-inteligencia-artificial-inicia-se-esta-semana
-https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal</t>
+          <t>[oficial] https://www.portugal.gov.pt/pt/gc24/comunicacao/noticia?i=auscultacao-para-a-agenda-nacional-de-inteligencia-artificial-inicia-se-esta-semana
+[secundaria] https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1191,8 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/</t>
+          <t>[oficial] https://www.compete2030.gov.pt/comunicacao/portugal-prepara-agenda-nacional-de-inteligencia-artificial/
+[secundaria] https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal</t>
         </is>
       </c>
     </row>
@@ -1221,9 +1224,9 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250
-https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791
-https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal</t>
+          <t>[oficial] https://oecd.ai/en/dashboards/policy-initiatives/ai-portugal-2030-national-strategy-for-ai-1250
+[secundaria] https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791
+[secundaria] https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1258,8 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016</t>
+          <t>[oficial] https://diariodarepublica.pt/dr/detalhe/resolucao-conselho-ministros/2-2026-1000882016
+[oficial] https://digital.gov.pt/pt/documentos/resolucao-do-conselho-de-ministros-2-2026</t>
         </is>
       </c>
     </row>
@@ -1294,8 +1298,8 @@
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/6794475.html?view=participation
-https://jtc1info.org/sd-2-history/jtc1-subcommittees/sc-42/</t>
+          <t>[oficial] https://www.iso.org/committee/6794475.html?view=participation
+[secundaria] https://jtc1info.org/sd-2-history/jtc1-subcommittees/sc-42/</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1331,8 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>https://www.iso.org/committee/45306.html?view=participation</t>
+          <t>[oficial] https://www.iso.org/committee/45306.html?view=participation
+[secundaria] https://en.wikipedia.org/wiki/ISO/IEC_JTC_1/SC_27</t>
         </is>
       </c>
     </row>
@@ -1359,8 +1364,8 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>https://oecd.ai/en/ai-principles
-https://www.unesco.org/en/artificial-intelligence/recommendation-ethics</t>
+          <t>[oficial] https://oecd.ai/en/ai-principles
+[oficial] https://www.unesco.org/en/artificial-intelligence/recommendation-ethics</t>
         </is>
       </c>
     </row>
@@ -1399,9 +1404,9 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791
-https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal
-https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
+          <t>[oficial] https://eur-lex.europa.eu/eli/reg/2024/1689/oj
+[secundaria] https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791
+[secundaria] https://cms.law/en/int/expert-guides/ai-regulation-scanner/portugal</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1438,8 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/eli/reg/2024/1689/oj</t>
+          <t>[oficial] https://eur-lex.europa.eu/eli/reg/2024/1689/oj
+[secundaria] https://artificialintelligenceact.eu</t>
         </is>
       </c>
     </row>
@@ -1465,8 +1471,8 @@
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>https://artificialintelligenceact.eu/article/57
-https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791</t>
+          <t>[secundaria] https://artificialintelligenceact.eu/article/57
+[secundaria] https://www.publico.pt/2025/09/19/ciencia/noticia/anacom-sera-reguladora-inteligencia-artificial-portugal-anuncia-governo-2147791</t>
         </is>
       </c>
     </row>
@@ -1498,8 +1504,8 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>https://www.dlapiperdataprotection.com/?t=law&amp;c=PT
-https://www.cnpd.pt</t>
+          <t>[oficial] https://www.cnpd.pt
+[secundaria] https://www.dlapiperdataprotection.com/?t=law&amp;c=PT</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1537,8 @@
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>https://www.cnpd.pt</t>
+          <t>[oficial] https://www.cnpd.pt
+[secundaria] https://www.dlapiperdataprotection.com/?t=authority&amp;c=PT</t>
         </is>
       </c>
     </row>
@@ -1570,8 +1577,8 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1603,8 +1610,8 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1636,8 +1643,8 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1669,8 +1676,8 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1702,8 +1709,8 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
-https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
+          <t>[oficial] https://www.itu.int/epublications/publication/global-cybersecurity-index-2024
+[oficial] https://data360.worldbank.org/en/indicator/ITU_GCI_GCI_OVRL_SCRE</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1742,8 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>https://www.global-index.ai</t>
+          <t>[oficial] https://www.global-index.ai
+[secundaria] https://girai-report-2024-corrected-edition.tiiny.site/</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1775,8 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>https://www.global-index.ai</t>
+          <t>[oficial] https://www.global-index.ai
+[oficial] https://www.globalcenter.ai/</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1808,8 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>https://networkreadinessindex.org/country/portugal/</t>
+          <t>[oficial] https://networkreadinessindex.org/country/portugal/
+[oficial] https://download.networkreadinessindex.org/reports/data/2025/nri-2025.pdf</t>
         </is>
       </c>
     </row>
@@ -1831,8 +1841,8 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
-https://ember-energy.org/data/electricity-data-explorer/</t>
+          <t>[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
+[oficial] https://ember-energy.org/data/electricity-data-explorer/</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/por_pais/Gobernanza_PT_Portugal_ILIA2026.xlsx
+++ b/data/paises_extra/por_pais/Gobernanza_PT_Portugal_ILIA2026.xlsx
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>80,90%</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1836,13 +1836,13 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>85,19 % (2024) / 80,95 % (2025) renovable total. Excl. toda hidro 53,69 %; hidro 31,50 % → si ILIA excluyera gran hidro, baja mucho.  [confianza: ALTA]</t>
+          <t>Energía limpia 2025 = 80,90 % (renovables 80,90 % + nuclear 0; incl. hidro 29,72 %). EMBER, determinístico (renov 41,37/51,14 TWh). A confirmar con CENIA.  [confianza: ALTA]</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv
-[oficial] https://ember-energy.org/data/electricity-data-explorer/</t>
+          <t>[oficial] https://ember-energy.org/data/electricity-data-explorer/
+[oficial] https://raw.githubusercontent.com/owid/energy-data/master/owid-energy-data.csv</t>
         </is>
       </c>
     </row>
